--- a/מצבת_משרד_המשפטים_מאוחדת.xlsx
+++ b/מצבת_משרד_המשפטים_מאוחדת.xlsx
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -147,6 +147,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6348,9 +6351,9 @@
           <t>אזור התעשיה סכנין</t>
         </is>
       </c>
-      <c r="X56" s="7" t="inlineStr">
-        <is>
-          <t>הושלם</t>
+      <c r="X56" s="12" t="inlineStr">
+        <is>
+          <t>כפילות במקור - לאימות</t>
         </is>
       </c>
     </row>
@@ -18131,9 +18134,9 @@
           <t>תאופיק זיאד נצרת</t>
         </is>
       </c>
-      <c r="X170" s="7" t="inlineStr">
-        <is>
-          <t>הושלם</t>
+      <c r="X170" s="12" t="inlineStr">
+        <is>
+          <t>כפילות במקור - לאימות</t>
         </is>
       </c>
     </row>
@@ -26847,9 +26850,9 @@
           <t>אופנהיימר 10</t>
         </is>
       </c>
-      <c r="X264" s="7" t="inlineStr">
-        <is>
-          <t>הושלם</t>
+      <c r="X264" s="12" t="inlineStr">
+        <is>
+          <t>כפילות במקור - לאימות</t>
         </is>
       </c>
     </row>
@@ -29973,9 +29976,9 @@
           <t>אלפל 16, סח'נין</t>
         </is>
       </c>
-      <c r="X296" s="7" t="inlineStr">
-        <is>
-          <t>הושלם</t>
+      <c r="X296" s="12" t="inlineStr">
+        <is>
+          <t>כפילות במקור - לאימות</t>
         </is>
       </c>
     </row>
